--- a/import/csvformat/Geschäftsparter-Import-Vorlage-deutsch.xlsx
+++ b/import/csvformat/Geschäftsparter-Import-Vorlage-deutsch.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Geschäftsparter" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Unterreiter-Kunde" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Unterreiter-Lieferant" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Unterreiter-Bankverbindung" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Unterreiter-Anschrift" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Unterreiter-Kontaktperson" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Geschäftsparter" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Unterreiter-Kunde" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Unterreiter-Lieferant" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Unterreiter-Bankverbindung" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Unterreiter-Anschrift" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Unterreiter-Kontaktperson" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="165">
   <si>
     <t xml:space="preserve">Search Key</t>
   </si>
@@ -338,6 +338,9 @@
     <t xml:space="preserve">Deviant Business Partner Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Print Contact Name (Y/N)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adress 1st line</t>
   </si>
   <si>
@@ -362,19 +365,19 @@
     <t xml:space="preserve">Fax</t>
   </si>
   <si>
+    <t xml:space="preserve">Mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mail(CC)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ship to Address (Y/N)</t>
   </si>
   <si>
     <t xml:space="preserve">Invoice to Address (Y/N)</t>
   </si>
   <si>
-    <t xml:space="preserve">Remit to Address (Y/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay from Address  (Y/N)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax Location (Y/N)</t>
+    <t xml:space="preserve">Invoice by Email (Y/N)</t>
   </si>
   <si>
     <t xml:space="preserve">Isheadquarter  (Y/N)</t>
@@ -383,16 +386,25 @@
     <t xml:space="preserve">VAT-Number </t>
   </si>
   <si>
+    <t xml:space="preserve">EORI Number</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tax</t>
   </si>
   <si>
     <t xml:space="preserve">Sales Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice Receiver (Bpartner Value)</t>
   </si>
   <si>
     <t xml:space="preserve">Abweichender 
 Geschäftspartner Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontaktperson drucken</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Zeile</t>
   </si>
   <si>
@@ -417,16 +429,7 @@
     <t xml:space="preserve">Rechnungsanschrift</t>
   </si>
   <si>
-    <t xml:space="preserve">Zahlungsanschrift 
-(ausgeblendet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahnungsanschrift 
-(ausgeblendet)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steueranschrift 
-(ausgeblendet)</t>
+    <t xml:space="preserve">Rechnung per EMail</t>
   </si>
   <si>
     <t xml:space="preserve">Hauptsitz</t>
@@ -436,13 +439,18 @@
 ID-Nummer</t>
   </si>
   <si>
-    <t xml:space="preserve">Steuer (NUR bei 
-Auslands-Adressen!!!)</t>
+    <t xml:space="preserve">EORI Zoll - Kennummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steuer (NUR bei Auslands-Adressen!!!)</t>
   </si>
   <si>
     <t xml:space="preserve">Vertriebsgebiet</t>
   </si>
   <si>
+    <t xml:space="preserve">Rechnungsempfänger</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metzer Str. 5</t>
   </si>
   <si>
@@ -453,6 +461,15 @@
   </si>
   <si>
     <t xml:space="preserve">0421-89009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@kunde1.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info-cc@kunde1.de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE123456789</t>
   </si>
   <si>
     <t xml:space="preserve">Greeting</t>
@@ -493,9 +510,6 @@
   </si>
   <si>
     <t xml:space="preserve">Titel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mail</t>
   </si>
   <si>
     <t xml:space="preserve">Kommentar</t>
@@ -526,7 +540,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -547,6 +561,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -591,8 +617,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -604,155 +642,273 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="31.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="28.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9.03"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="31.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="28.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="22.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
@@ -761,170 +917,170 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="19.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.3"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="17" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="13.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="17" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
@@ -933,95 +1089,95 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="18.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>70000</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
@@ -1030,127 +1186,127 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.4"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="12" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="22.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>99</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
@@ -1159,34 +1315,37 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMK4"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="21.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="19.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="21" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="20.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="19.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="14.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="22.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="24" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1197,10 +1356,10 @@
         <v>100</v>
       </c>
       <c r="C1" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>101</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>102</v>
@@ -1250,121 +1409,1159 @@
       <c r="T1" s="0" t="s">
         <v>117</v>
       </c>
+      <c r="U1" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="V1" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="W1" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="X1" s="0"/>
+      <c r="Y1" s="0"/>
+      <c r="Z1" s="0"/>
+      <c r="AA1" s="0"/>
+      <c r="AB1" s="0"/>
+      <c r="AC1" s="0"/>
+      <c r="AD1" s="0"/>
+      <c r="AE1" s="0"/>
+      <c r="AF1" s="0"/>
+      <c r="AG1" s="0"/>
+      <c r="AH1" s="0"/>
+      <c r="AI1" s="0"/>
+      <c r="AJ1" s="0"/>
+      <c r="AK1" s="0"/>
+      <c r="AL1" s="0"/>
+      <c r="AM1" s="0"/>
+      <c r="AN1" s="0"/>
+      <c r="AO1" s="0"/>
+      <c r="AP1" s="0"/>
+      <c r="AQ1" s="0"/>
+      <c r="AR1" s="0"/>
+      <c r="AS1" s="0"/>
+      <c r="AT1" s="0"/>
+      <c r="AU1" s="0"/>
+      <c r="AV1" s="0"/>
+      <c r="AW1" s="0"/>
+      <c r="AX1" s="0"/>
+      <c r="AY1" s="0"/>
+      <c r="AZ1" s="0"/>
+      <c r="BA1" s="0"/>
+      <c r="BB1" s="0"/>
+      <c r="BC1" s="0"/>
+      <c r="BD1" s="0"/>
+      <c r="BE1" s="0"/>
+      <c r="BF1" s="0"/>
+      <c r="BG1" s="0"/>
+      <c r="BH1" s="0"/>
+      <c r="BI1" s="0"/>
+      <c r="BJ1" s="0"/>
+      <c r="BK1" s="0"/>
+      <c r="BL1" s="0"/>
+      <c r="BM1" s="0"/>
+      <c r="BN1" s="0"/>
+      <c r="BO1" s="0"/>
+      <c r="BP1" s="0"/>
+      <c r="BQ1" s="0"/>
+      <c r="BR1" s="0"/>
+      <c r="BS1" s="0"/>
+      <c r="BT1" s="0"/>
+      <c r="BU1" s="0"/>
+      <c r="BV1" s="0"/>
+      <c r="BW1" s="0"/>
+      <c r="BX1" s="0"/>
+      <c r="BY1" s="0"/>
+      <c r="BZ1" s="0"/>
+      <c r="CA1" s="0"/>
+      <c r="CB1" s="0"/>
+      <c r="CC1" s="0"/>
+      <c r="CD1" s="0"/>
+      <c r="CE1" s="0"/>
+      <c r="CF1" s="0"/>
+      <c r="CG1" s="0"/>
+      <c r="CH1" s="0"/>
+      <c r="CI1" s="0"/>
+      <c r="CJ1" s="0"/>
+      <c r="CK1" s="0"/>
+      <c r="CL1" s="0"/>
+      <c r="CM1" s="0"/>
+      <c r="CN1" s="0"/>
+      <c r="CO1" s="0"/>
+      <c r="CP1" s="0"/>
+      <c r="CQ1" s="0"/>
+      <c r="CR1" s="0"/>
+      <c r="CS1" s="0"/>
+      <c r="CT1" s="0"/>
+      <c r="CU1" s="0"/>
+      <c r="CV1" s="0"/>
+      <c r="CW1" s="0"/>
+      <c r="CX1" s="0"/>
+      <c r="CY1" s="0"/>
+      <c r="CZ1" s="0"/>
+      <c r="DA1" s="0"/>
+      <c r="DB1" s="0"/>
+      <c r="DC1" s="0"/>
+      <c r="DD1" s="0"/>
+      <c r="DE1" s="0"/>
+      <c r="DF1" s="0"/>
+      <c r="DG1" s="0"/>
+      <c r="DH1" s="0"/>
+      <c r="DI1" s="0"/>
+      <c r="DJ1" s="0"/>
+      <c r="DK1" s="0"/>
+      <c r="DL1" s="0"/>
+      <c r="DM1" s="0"/>
+      <c r="DN1" s="0"/>
+      <c r="DO1" s="0"/>
+      <c r="DP1" s="0"/>
+      <c r="DQ1" s="0"/>
+      <c r="DR1" s="0"/>
+      <c r="DS1" s="0"/>
+      <c r="DT1" s="0"/>
+      <c r="DU1" s="0"/>
+      <c r="DV1" s="0"/>
+      <c r="DW1" s="0"/>
+      <c r="DX1" s="0"/>
+      <c r="DY1" s="0"/>
+      <c r="DZ1" s="0"/>
+      <c r="EA1" s="0"/>
+      <c r="EB1" s="0"/>
+      <c r="EC1" s="0"/>
+      <c r="ED1" s="0"/>
+      <c r="EE1" s="0"/>
+      <c r="EF1" s="0"/>
+      <c r="EG1" s="0"/>
+      <c r="EH1" s="0"/>
+      <c r="EI1" s="0"/>
+      <c r="EJ1" s="0"/>
+      <c r="EK1" s="0"/>
+      <c r="EL1" s="0"/>
+      <c r="EM1" s="0"/>
+      <c r="EN1" s="0"/>
+      <c r="EO1" s="0"/>
+      <c r="EP1" s="0"/>
+      <c r="EQ1" s="0"/>
+      <c r="ER1" s="0"/>
+      <c r="ES1" s="0"/>
+      <c r="ET1" s="0"/>
+      <c r="EU1" s="0"/>
+      <c r="EV1" s="0"/>
+      <c r="EW1" s="0"/>
+      <c r="EX1" s="0"/>
+      <c r="EY1" s="0"/>
+      <c r="EZ1" s="0"/>
+      <c r="FA1" s="0"/>
+      <c r="FB1" s="0"/>
+      <c r="FC1" s="0"/>
+      <c r="FD1" s="0"/>
+      <c r="FE1" s="0"/>
+      <c r="FF1" s="0"/>
+      <c r="FG1" s="0"/>
+      <c r="FH1" s="0"/>
+      <c r="FI1" s="0"/>
+      <c r="FJ1" s="0"/>
+      <c r="FK1" s="0"/>
+      <c r="FL1" s="0"/>
+      <c r="FM1" s="0"/>
+      <c r="FN1" s="0"/>
+      <c r="FO1" s="0"/>
+      <c r="FP1" s="0"/>
+      <c r="FQ1" s="0"/>
+      <c r="FR1" s="0"/>
+      <c r="FS1" s="0"/>
+      <c r="FT1" s="0"/>
+      <c r="FU1" s="0"/>
+      <c r="FV1" s="0"/>
+      <c r="FW1" s="0"/>
+      <c r="FX1" s="0"/>
+      <c r="FY1" s="0"/>
+      <c r="FZ1" s="0"/>
+      <c r="GA1" s="0"/>
+      <c r="GB1" s="0"/>
+      <c r="GC1" s="0"/>
+      <c r="GD1" s="0"/>
+      <c r="GE1" s="0"/>
+      <c r="GF1" s="0"/>
+      <c r="GG1" s="0"/>
+      <c r="GH1" s="0"/>
+      <c r="GI1" s="0"/>
+      <c r="GJ1" s="0"/>
+      <c r="GK1" s="0"/>
+      <c r="GL1" s="0"/>
+      <c r="GM1" s="0"/>
+      <c r="GN1" s="0"/>
+      <c r="GO1" s="0"/>
+      <c r="GP1" s="0"/>
+      <c r="GQ1" s="0"/>
+      <c r="GR1" s="0"/>
+      <c r="GS1" s="0"/>
+      <c r="GT1" s="0"/>
+      <c r="GU1" s="0"/>
+      <c r="GV1" s="0"/>
+      <c r="GW1" s="0"/>
+      <c r="GX1" s="0"/>
+      <c r="GY1" s="0"/>
+      <c r="GZ1" s="0"/>
+      <c r="HA1" s="0"/>
+      <c r="HB1" s="0"/>
+      <c r="HC1" s="0"/>
+      <c r="HD1" s="0"/>
+      <c r="HE1" s="0"/>
+      <c r="HF1" s="0"/>
+      <c r="HG1" s="0"/>
+      <c r="HH1" s="0"/>
+      <c r="HI1" s="0"/>
+      <c r="HJ1" s="0"/>
+      <c r="HK1" s="0"/>
+      <c r="HL1" s="0"/>
+      <c r="HM1" s="0"/>
+      <c r="HN1" s="0"/>
+      <c r="HO1" s="0"/>
+      <c r="HP1" s="0"/>
+      <c r="HQ1" s="0"/>
+      <c r="HR1" s="0"/>
+      <c r="HS1" s="0"/>
+      <c r="HT1" s="0"/>
+      <c r="HU1" s="0"/>
+      <c r="HV1" s="0"/>
+      <c r="HW1" s="0"/>
+      <c r="HX1" s="0"/>
+      <c r="HY1" s="0"/>
+      <c r="HZ1" s="0"/>
+      <c r="IA1" s="0"/>
+      <c r="IB1" s="0"/>
+      <c r="IC1" s="0"/>
+      <c r="ID1" s="0"/>
+      <c r="IE1" s="0"/>
+      <c r="IF1" s="0"/>
+      <c r="IG1" s="0"/>
+      <c r="IH1" s="0"/>
+      <c r="II1" s="0"/>
+      <c r="IJ1" s="0"/>
+      <c r="IK1" s="0"/>
+      <c r="IL1" s="0"/>
+      <c r="IM1" s="0"/>
+      <c r="IN1" s="0"/>
+      <c r="IO1" s="0"/>
+      <c r="IP1" s="0"/>
+      <c r="IQ1" s="0"/>
+      <c r="IR1" s="0"/>
+      <c r="IS1" s="0"/>
+      <c r="IT1" s="0"/>
+      <c r="IU1" s="0"/>
+      <c r="IV1" s="0"/>
+      <c r="IW1" s="0"/>
+      <c r="IX1" s="0"/>
+      <c r="IY1" s="0"/>
+      <c r="IZ1" s="0"/>
+      <c r="JA1" s="0"/>
+      <c r="JB1" s="0"/>
+      <c r="JC1" s="0"/>
+      <c r="JD1" s="0"/>
+      <c r="JE1" s="0"/>
+      <c r="JF1" s="0"/>
+      <c r="JG1" s="0"/>
+      <c r="JH1" s="0"/>
+      <c r="JI1" s="0"/>
+      <c r="JJ1" s="0"/>
+      <c r="JK1" s="0"/>
+      <c r="JL1" s="0"/>
+      <c r="JM1" s="0"/>
+      <c r="JN1" s="0"/>
+      <c r="JO1" s="0"/>
+      <c r="JP1" s="0"/>
+      <c r="JQ1" s="0"/>
+      <c r="JR1" s="0"/>
+      <c r="JS1" s="0"/>
+      <c r="JT1" s="0"/>
+      <c r="JU1" s="0"/>
+      <c r="JV1" s="0"/>
+      <c r="JW1" s="0"/>
+      <c r="JX1" s="0"/>
+      <c r="JY1" s="0"/>
+      <c r="JZ1" s="0"/>
+      <c r="KA1" s="0"/>
+      <c r="KB1" s="0"/>
+      <c r="KC1" s="0"/>
+      <c r="KD1" s="0"/>
+      <c r="KE1" s="0"/>
+      <c r="KF1" s="0"/>
+      <c r="KG1" s="0"/>
+      <c r="KH1" s="0"/>
+      <c r="KI1" s="0"/>
+      <c r="KJ1" s="0"/>
+      <c r="KK1" s="0"/>
+      <c r="KL1" s="0"/>
+      <c r="KM1" s="0"/>
+      <c r="KN1" s="0"/>
+      <c r="KO1" s="0"/>
+      <c r="KP1" s="0"/>
+      <c r="KQ1" s="0"/>
+      <c r="KR1" s="0"/>
+      <c r="KS1" s="0"/>
+      <c r="KT1" s="0"/>
+      <c r="KU1" s="0"/>
+      <c r="KV1" s="0"/>
+      <c r="KW1" s="0"/>
+      <c r="KX1" s="0"/>
+      <c r="KY1" s="0"/>
+      <c r="KZ1" s="0"/>
+      <c r="LA1" s="0"/>
+      <c r="LB1" s="0"/>
+      <c r="LC1" s="0"/>
+      <c r="LD1" s="0"/>
+      <c r="LE1" s="0"/>
+      <c r="LF1" s="0"/>
+      <c r="LG1" s="0"/>
+      <c r="LH1" s="0"/>
+      <c r="LI1" s="0"/>
+      <c r="LJ1" s="0"/>
+      <c r="LK1" s="0"/>
+      <c r="LL1" s="0"/>
+      <c r="LM1" s="0"/>
+      <c r="LN1" s="0"/>
+      <c r="LO1" s="0"/>
+      <c r="LP1" s="0"/>
+      <c r="LQ1" s="0"/>
+      <c r="LR1" s="0"/>
+      <c r="LS1" s="0"/>
+      <c r="LT1" s="0"/>
+      <c r="LU1" s="0"/>
+      <c r="LV1" s="0"/>
+      <c r="LW1" s="0"/>
+      <c r="LX1" s="0"/>
+      <c r="LY1" s="0"/>
+      <c r="LZ1" s="0"/>
+      <c r="MA1" s="0"/>
+      <c r="MB1" s="0"/>
+      <c r="MC1" s="0"/>
+      <c r="MD1" s="0"/>
+      <c r="ME1" s="0"/>
+      <c r="MF1" s="0"/>
+      <c r="MG1" s="0"/>
+      <c r="MH1" s="0"/>
+      <c r="MI1" s="0"/>
+      <c r="MJ1" s="0"/>
+      <c r="MK1" s="0"/>
+      <c r="ML1" s="0"/>
+      <c r="MM1" s="0"/>
+      <c r="MN1" s="0"/>
+      <c r="MO1" s="0"/>
+      <c r="MP1" s="0"/>
+      <c r="MQ1" s="0"/>
+      <c r="MR1" s="0"/>
+      <c r="MS1" s="0"/>
+      <c r="MT1" s="0"/>
+      <c r="MU1" s="0"/>
+      <c r="MV1" s="0"/>
+      <c r="MW1" s="0"/>
+      <c r="MX1" s="0"/>
+      <c r="MY1" s="0"/>
+      <c r="MZ1" s="0"/>
+      <c r="NA1" s="0"/>
+      <c r="NB1" s="0"/>
+      <c r="NC1" s="0"/>
+      <c r="ND1" s="0"/>
+      <c r="NE1" s="0"/>
+      <c r="NF1" s="0"/>
+      <c r="NG1" s="0"/>
+      <c r="NH1" s="0"/>
+      <c r="NI1" s="0"/>
+      <c r="NJ1" s="0"/>
+      <c r="NK1" s="0"/>
+      <c r="NL1" s="0"/>
+      <c r="NM1" s="0"/>
+      <c r="NN1" s="0"/>
+      <c r="NO1" s="0"/>
+      <c r="NP1" s="0"/>
+      <c r="NQ1" s="0"/>
+      <c r="NR1" s="0"/>
+      <c r="NS1" s="0"/>
+      <c r="NT1" s="0"/>
+      <c r="NU1" s="0"/>
+      <c r="NV1" s="0"/>
+      <c r="NW1" s="0"/>
+      <c r="NX1" s="0"/>
+      <c r="NY1" s="0"/>
+      <c r="NZ1" s="0"/>
+      <c r="OA1" s="0"/>
+      <c r="OB1" s="0"/>
+      <c r="OC1" s="0"/>
+      <c r="OD1" s="0"/>
+      <c r="OE1" s="0"/>
+      <c r="OF1" s="0"/>
+      <c r="OG1" s="0"/>
+      <c r="OH1" s="0"/>
+      <c r="OI1" s="0"/>
+      <c r="OJ1" s="0"/>
+      <c r="OK1" s="0"/>
+      <c r="OL1" s="0"/>
+      <c r="OM1" s="0"/>
+      <c r="ON1" s="0"/>
+      <c r="OO1" s="0"/>
+      <c r="OP1" s="0"/>
+      <c r="OQ1" s="0"/>
+      <c r="OR1" s="0"/>
+      <c r="OS1" s="0"/>
+      <c r="OT1" s="0"/>
+      <c r="OU1" s="0"/>
+      <c r="OV1" s="0"/>
+      <c r="OW1" s="0"/>
+      <c r="OX1" s="0"/>
+      <c r="OY1" s="0"/>
+      <c r="OZ1" s="0"/>
+      <c r="PA1" s="0"/>
+      <c r="PB1" s="0"/>
+      <c r="PC1" s="0"/>
+      <c r="PD1" s="0"/>
+      <c r="PE1" s="0"/>
+      <c r="PF1" s="0"/>
+      <c r="PG1" s="0"/>
+      <c r="PH1" s="0"/>
+      <c r="PI1" s="0"/>
+      <c r="PJ1" s="0"/>
+      <c r="PK1" s="0"/>
+      <c r="PL1" s="0"/>
+      <c r="PM1" s="0"/>
+      <c r="PN1" s="0"/>
+      <c r="PO1" s="0"/>
+      <c r="PP1" s="0"/>
+      <c r="PQ1" s="0"/>
+      <c r="PR1" s="0"/>
+      <c r="PS1" s="0"/>
+      <c r="PT1" s="0"/>
+      <c r="PU1" s="0"/>
+      <c r="PV1" s="0"/>
+      <c r="PW1" s="0"/>
+      <c r="PX1" s="0"/>
+      <c r="PY1" s="0"/>
+      <c r="PZ1" s="0"/>
+      <c r="QA1" s="0"/>
+      <c r="QB1" s="0"/>
+      <c r="QC1" s="0"/>
+      <c r="QD1" s="0"/>
+      <c r="QE1" s="0"/>
+      <c r="QF1" s="0"/>
+      <c r="QG1" s="0"/>
+      <c r="QH1" s="0"/>
+      <c r="QI1" s="0"/>
+      <c r="QJ1" s="0"/>
+      <c r="QK1" s="0"/>
+      <c r="QL1" s="0"/>
+      <c r="QM1" s="0"/>
+      <c r="QN1" s="0"/>
+      <c r="QO1" s="0"/>
+      <c r="QP1" s="0"/>
+      <c r="QQ1" s="0"/>
+      <c r="QR1" s="0"/>
+      <c r="QS1" s="0"/>
+      <c r="QT1" s="0"/>
+      <c r="QU1" s="0"/>
+      <c r="QV1" s="0"/>
+      <c r="QW1" s="0"/>
+      <c r="QX1" s="0"/>
+      <c r="QY1" s="0"/>
+      <c r="QZ1" s="0"/>
+      <c r="RA1" s="0"/>
+      <c r="RB1" s="0"/>
+      <c r="RC1" s="0"/>
+      <c r="RD1" s="0"/>
+      <c r="RE1" s="0"/>
+      <c r="RF1" s="0"/>
+      <c r="RG1" s="0"/>
+      <c r="RH1" s="0"/>
+      <c r="RI1" s="0"/>
+      <c r="RJ1" s="0"/>
+      <c r="RK1" s="0"/>
+      <c r="RL1" s="0"/>
+      <c r="RM1" s="0"/>
+      <c r="RN1" s="0"/>
+      <c r="RO1" s="0"/>
+      <c r="RP1" s="0"/>
+      <c r="RQ1" s="0"/>
+      <c r="RR1" s="0"/>
+      <c r="RS1" s="0"/>
+      <c r="RT1" s="0"/>
+      <c r="RU1" s="0"/>
+      <c r="RV1" s="0"/>
+      <c r="RW1" s="0"/>
+      <c r="RX1" s="0"/>
+      <c r="RY1" s="0"/>
+      <c r="RZ1" s="0"/>
+      <c r="SA1" s="0"/>
+      <c r="SB1" s="0"/>
+      <c r="SC1" s="0"/>
+      <c r="SD1" s="0"/>
+      <c r="SE1" s="0"/>
+      <c r="SF1" s="0"/>
+      <c r="SG1" s="0"/>
+      <c r="SH1" s="0"/>
+      <c r="SI1" s="0"/>
+      <c r="SJ1" s="0"/>
+      <c r="SK1" s="0"/>
+      <c r="SL1" s="0"/>
+      <c r="SM1" s="0"/>
+      <c r="SN1" s="0"/>
+      <c r="SO1" s="0"/>
+      <c r="SP1" s="0"/>
+      <c r="SQ1" s="0"/>
+      <c r="SR1" s="0"/>
+      <c r="SS1" s="0"/>
+      <c r="ST1" s="0"/>
+      <c r="SU1" s="0"/>
+      <c r="SV1" s="0"/>
+      <c r="SW1" s="0"/>
+      <c r="SX1" s="0"/>
+      <c r="SY1" s="0"/>
+      <c r="SZ1" s="0"/>
+      <c r="TA1" s="0"/>
+      <c r="TB1" s="0"/>
+      <c r="TC1" s="0"/>
+      <c r="TD1" s="0"/>
+      <c r="TE1" s="0"/>
+      <c r="TF1" s="0"/>
+      <c r="TG1" s="0"/>
+      <c r="TH1" s="0"/>
+      <c r="TI1" s="0"/>
+      <c r="TJ1" s="0"/>
+      <c r="TK1" s="0"/>
+      <c r="TL1" s="0"/>
+      <c r="TM1" s="0"/>
+      <c r="TN1" s="0"/>
+      <c r="TO1" s="0"/>
+      <c r="TP1" s="0"/>
+      <c r="TQ1" s="0"/>
+      <c r="TR1" s="0"/>
+      <c r="TS1" s="0"/>
+      <c r="TT1" s="0"/>
+      <c r="TU1" s="0"/>
+      <c r="TV1" s="0"/>
+      <c r="TW1" s="0"/>
+      <c r="TX1" s="0"/>
+      <c r="TY1" s="0"/>
+      <c r="TZ1" s="0"/>
+      <c r="UA1" s="0"/>
+      <c r="UB1" s="0"/>
+      <c r="UC1" s="0"/>
+      <c r="UD1" s="0"/>
+      <c r="UE1" s="0"/>
+      <c r="UF1" s="0"/>
+      <c r="UG1" s="0"/>
+      <c r="UH1" s="0"/>
+      <c r="UI1" s="0"/>
+      <c r="UJ1" s="0"/>
+      <c r="UK1" s="0"/>
+      <c r="UL1" s="0"/>
+      <c r="UM1" s="0"/>
+      <c r="UN1" s="0"/>
+      <c r="UO1" s="0"/>
+      <c r="UP1" s="0"/>
+      <c r="UQ1" s="0"/>
+      <c r="UR1" s="0"/>
+      <c r="US1" s="0"/>
+      <c r="UT1" s="0"/>
+      <c r="UU1" s="0"/>
+      <c r="UV1" s="0"/>
+      <c r="UW1" s="0"/>
+      <c r="UX1" s="0"/>
+      <c r="UY1" s="0"/>
+      <c r="UZ1" s="0"/>
+      <c r="VA1" s="0"/>
+      <c r="VB1" s="0"/>
+      <c r="VC1" s="0"/>
+      <c r="VD1" s="0"/>
+      <c r="VE1" s="0"/>
+      <c r="VF1" s="0"/>
+      <c r="VG1" s="0"/>
+      <c r="VH1" s="0"/>
+      <c r="VI1" s="0"/>
+      <c r="VJ1" s="0"/>
+      <c r="VK1" s="0"/>
+      <c r="VL1" s="0"/>
+      <c r="VM1" s="0"/>
+      <c r="VN1" s="0"/>
+      <c r="VO1" s="0"/>
+      <c r="VP1" s="0"/>
+      <c r="VQ1" s="0"/>
+      <c r="VR1" s="0"/>
+      <c r="VS1" s="0"/>
+      <c r="VT1" s="0"/>
+      <c r="VU1" s="0"/>
+      <c r="VV1" s="0"/>
+      <c r="VW1" s="0"/>
+      <c r="VX1" s="0"/>
+      <c r="VY1" s="0"/>
+      <c r="VZ1" s="0"/>
+      <c r="WA1" s="0"/>
+      <c r="WB1" s="0"/>
+      <c r="WC1" s="0"/>
+      <c r="WD1" s="0"/>
+      <c r="WE1" s="0"/>
+      <c r="WF1" s="0"/>
+      <c r="WG1" s="0"/>
+      <c r="WH1" s="0"/>
+      <c r="WI1" s="0"/>
+      <c r="WJ1" s="0"/>
+      <c r="WK1" s="0"/>
+      <c r="WL1" s="0"/>
+      <c r="WM1" s="0"/>
+      <c r="WN1" s="0"/>
+      <c r="WO1" s="0"/>
+      <c r="WP1" s="0"/>
+      <c r="WQ1" s="0"/>
+      <c r="WR1" s="0"/>
+      <c r="WS1" s="0"/>
+      <c r="WT1" s="0"/>
+      <c r="WU1" s="0"/>
+      <c r="WV1" s="0"/>
+      <c r="WW1" s="0"/>
+      <c r="WX1" s="0"/>
+      <c r="WY1" s="0"/>
+      <c r="WZ1" s="0"/>
+      <c r="XA1" s="0"/>
+      <c r="XB1" s="0"/>
+      <c r="XC1" s="0"/>
+      <c r="XD1" s="0"/>
+      <c r="XE1" s="0"/>
+      <c r="XF1" s="0"/>
+      <c r="XG1" s="0"/>
+      <c r="XH1" s="0"/>
+      <c r="XI1" s="0"/>
+      <c r="XJ1" s="0"/>
+      <c r="XK1" s="0"/>
+      <c r="XL1" s="0"/>
+      <c r="XM1" s="0"/>
+      <c r="XN1" s="0"/>
+      <c r="XO1" s="0"/>
+      <c r="XP1" s="0"/>
+      <c r="XQ1" s="0"/>
+      <c r="XR1" s="0"/>
+      <c r="XS1" s="0"/>
+      <c r="XT1" s="0"/>
+      <c r="XU1" s="0"/>
+      <c r="XV1" s="0"/>
+      <c r="XW1" s="0"/>
+      <c r="XX1" s="0"/>
+      <c r="XY1" s="0"/>
+      <c r="XZ1" s="0"/>
+      <c r="YA1" s="0"/>
+      <c r="YB1" s="0"/>
+      <c r="YC1" s="0"/>
+      <c r="YD1" s="0"/>
+      <c r="YE1" s="0"/>
+      <c r="YF1" s="0"/>
+      <c r="YG1" s="0"/>
+      <c r="YH1" s="0"/>
+      <c r="YI1" s="0"/>
+      <c r="YJ1" s="0"/>
+      <c r="YK1" s="0"/>
+      <c r="YL1" s="0"/>
+      <c r="YM1" s="0"/>
+      <c r="YN1" s="0"/>
+      <c r="YO1" s="0"/>
+      <c r="YP1" s="0"/>
+      <c r="YQ1" s="0"/>
+      <c r="YR1" s="0"/>
+      <c r="YS1" s="0"/>
+      <c r="YT1" s="0"/>
+      <c r="YU1" s="0"/>
+      <c r="YV1" s="0"/>
+      <c r="YW1" s="0"/>
+      <c r="YX1" s="0"/>
+      <c r="YY1" s="0"/>
+      <c r="YZ1" s="0"/>
+      <c r="ZA1" s="0"/>
+      <c r="ZB1" s="0"/>
+      <c r="ZC1" s="0"/>
+      <c r="ZD1" s="0"/>
+      <c r="ZE1" s="0"/>
+      <c r="ZF1" s="0"/>
+      <c r="ZG1" s="0"/>
+      <c r="ZH1" s="0"/>
+      <c r="ZI1" s="0"/>
+      <c r="ZJ1" s="0"/>
+      <c r="ZK1" s="0"/>
+      <c r="ZL1" s="0"/>
+      <c r="ZM1" s="0"/>
+      <c r="ZN1" s="0"/>
+      <c r="ZO1" s="0"/>
+      <c r="ZP1" s="0"/>
+      <c r="ZQ1" s="0"/>
+      <c r="ZR1" s="0"/>
+      <c r="ZS1" s="0"/>
+      <c r="ZT1" s="0"/>
+      <c r="ZU1" s="0"/>
+      <c r="ZV1" s="0"/>
+      <c r="ZW1" s="0"/>
+      <c r="ZX1" s="0"/>
+      <c r="ZY1" s="0"/>
+      <c r="ZZ1" s="0"/>
+      <c r="AAA1" s="0"/>
+      <c r="AAB1" s="0"/>
+      <c r="AAC1" s="0"/>
+      <c r="AAD1" s="0"/>
+      <c r="AAE1" s="0"/>
+      <c r="AAF1" s="0"/>
+      <c r="AAG1" s="0"/>
+      <c r="AAH1" s="0"/>
+      <c r="AAI1" s="0"/>
+      <c r="AAJ1" s="0"/>
+      <c r="AAK1" s="0"/>
+      <c r="AAL1" s="0"/>
+      <c r="AAM1" s="0"/>
+      <c r="AAN1" s="0"/>
+      <c r="AAO1" s="0"/>
+      <c r="AAP1" s="0"/>
+      <c r="AAQ1" s="0"/>
+      <c r="AAR1" s="0"/>
+      <c r="AAS1" s="0"/>
+      <c r="AAT1" s="0"/>
+      <c r="AAU1" s="0"/>
+      <c r="AAV1" s="0"/>
+      <c r="AAW1" s="0"/>
+      <c r="AAX1" s="0"/>
+      <c r="AAY1" s="0"/>
+      <c r="AAZ1" s="0"/>
+      <c r="ABA1" s="0"/>
+      <c r="ABB1" s="0"/>
+      <c r="ABC1" s="0"/>
+      <c r="ABD1" s="0"/>
+      <c r="ABE1" s="0"/>
+      <c r="ABF1" s="0"/>
+      <c r="ABG1" s="0"/>
+      <c r="ABH1" s="0"/>
+      <c r="ABI1" s="0"/>
+      <c r="ABJ1" s="0"/>
+      <c r="ABK1" s="0"/>
+      <c r="ABL1" s="0"/>
+      <c r="ABM1" s="0"/>
+      <c r="ABN1" s="0"/>
+      <c r="ABO1" s="0"/>
+      <c r="ABP1" s="0"/>
+      <c r="ABQ1" s="0"/>
+      <c r="ABR1" s="0"/>
+      <c r="ABS1" s="0"/>
+      <c r="ABT1" s="0"/>
+      <c r="ABU1" s="0"/>
+      <c r="ABV1" s="0"/>
+      <c r="ABW1" s="0"/>
+      <c r="ABX1" s="0"/>
+      <c r="ABY1" s="0"/>
+      <c r="ABZ1" s="0"/>
+      <c r="ACA1" s="0"/>
+      <c r="ACB1" s="0"/>
+      <c r="ACC1" s="0"/>
+      <c r="ACD1" s="0"/>
+      <c r="ACE1" s="0"/>
+      <c r="ACF1" s="0"/>
+      <c r="ACG1" s="0"/>
+      <c r="ACH1" s="0"/>
+      <c r="ACI1" s="0"/>
+      <c r="ACJ1" s="0"/>
+      <c r="ACK1" s="0"/>
+      <c r="ACL1" s="0"/>
+      <c r="ACM1" s="0"/>
+      <c r="ACN1" s="0"/>
+      <c r="ACO1" s="0"/>
+      <c r="ACP1" s="0"/>
+      <c r="ACQ1" s="0"/>
+      <c r="ACR1" s="0"/>
+      <c r="ACS1" s="0"/>
+      <c r="ACT1" s="0"/>
+      <c r="ACU1" s="0"/>
+      <c r="ACV1" s="0"/>
+      <c r="ACW1" s="0"/>
+      <c r="ACX1" s="0"/>
+      <c r="ACY1" s="0"/>
+      <c r="ACZ1" s="0"/>
+      <c r="ADA1" s="0"/>
+      <c r="ADB1" s="0"/>
+      <c r="ADC1" s="0"/>
+      <c r="ADD1" s="0"/>
+      <c r="ADE1" s="0"/>
+      <c r="ADF1" s="0"/>
+      <c r="ADG1" s="0"/>
+      <c r="ADH1" s="0"/>
+      <c r="ADI1" s="0"/>
+      <c r="ADJ1" s="0"/>
+      <c r="ADK1" s="0"/>
+      <c r="ADL1" s="0"/>
+      <c r="ADM1" s="0"/>
+      <c r="ADN1" s="0"/>
+      <c r="ADO1" s="0"/>
+      <c r="ADP1" s="0"/>
+      <c r="ADQ1" s="0"/>
+      <c r="ADR1" s="0"/>
+      <c r="ADS1" s="0"/>
+      <c r="ADT1" s="0"/>
+      <c r="ADU1" s="0"/>
+      <c r="ADV1" s="0"/>
+      <c r="ADW1" s="0"/>
+      <c r="ADX1" s="0"/>
+      <c r="ADY1" s="0"/>
+      <c r="ADZ1" s="0"/>
+      <c r="AEA1" s="0"/>
+      <c r="AEB1" s="0"/>
+      <c r="AEC1" s="0"/>
+      <c r="AED1" s="0"/>
+      <c r="AEE1" s="0"/>
+      <c r="AEF1" s="0"/>
+      <c r="AEG1" s="0"/>
+      <c r="AEH1" s="0"/>
+      <c r="AEI1" s="0"/>
+      <c r="AEJ1" s="0"/>
+      <c r="AEK1" s="0"/>
+      <c r="AEL1" s="0"/>
+      <c r="AEM1" s="0"/>
+      <c r="AEN1" s="0"/>
+      <c r="AEO1" s="0"/>
+      <c r="AEP1" s="0"/>
+      <c r="AEQ1" s="0"/>
+      <c r="AER1" s="0"/>
+      <c r="AES1" s="0"/>
+      <c r="AET1" s="0"/>
+      <c r="AEU1" s="0"/>
+      <c r="AEV1" s="0"/>
+      <c r="AEW1" s="0"/>
+      <c r="AEX1" s="0"/>
+      <c r="AEY1" s="0"/>
+      <c r="AEZ1" s="0"/>
+      <c r="AFA1" s="0"/>
+      <c r="AFB1" s="0"/>
+      <c r="AFC1" s="0"/>
+      <c r="AFD1" s="0"/>
+      <c r="AFE1" s="0"/>
+      <c r="AFF1" s="0"/>
+      <c r="AFG1" s="0"/>
+      <c r="AFH1" s="0"/>
+      <c r="AFI1" s="0"/>
+      <c r="AFJ1" s="0"/>
+      <c r="AFK1" s="0"/>
+      <c r="AFL1" s="0"/>
+      <c r="AFM1" s="0"/>
+      <c r="AFN1" s="0"/>
+      <c r="AFO1" s="0"/>
+      <c r="AFP1" s="0"/>
+      <c r="AFQ1" s="0"/>
+      <c r="AFR1" s="0"/>
+      <c r="AFS1" s="0"/>
+      <c r="AFT1" s="0"/>
+      <c r="AFU1" s="0"/>
+      <c r="AFV1" s="0"/>
+      <c r="AFW1" s="0"/>
+      <c r="AFX1" s="0"/>
+      <c r="AFY1" s="0"/>
+      <c r="AFZ1" s="0"/>
+      <c r="AGA1" s="0"/>
+      <c r="AGB1" s="0"/>
+      <c r="AGC1" s="0"/>
+      <c r="AGD1" s="0"/>
+      <c r="AGE1" s="0"/>
+      <c r="AGF1" s="0"/>
+      <c r="AGG1" s="0"/>
+      <c r="AGH1" s="0"/>
+      <c r="AGI1" s="0"/>
+      <c r="AGJ1" s="0"/>
+      <c r="AGK1" s="0"/>
+      <c r="AGL1" s="0"/>
+      <c r="AGM1" s="0"/>
+      <c r="AGN1" s="0"/>
+      <c r="AGO1" s="0"/>
+      <c r="AGP1" s="0"/>
+      <c r="AGQ1" s="0"/>
+      <c r="AGR1" s="0"/>
+      <c r="AGS1" s="0"/>
+      <c r="AGT1" s="0"/>
+      <c r="AGU1" s="0"/>
+      <c r="AGV1" s="0"/>
+      <c r="AGW1" s="0"/>
+      <c r="AGX1" s="0"/>
+      <c r="AGY1" s="0"/>
+      <c r="AGZ1" s="0"/>
+      <c r="AHA1" s="0"/>
+      <c r="AHB1" s="0"/>
+      <c r="AHC1" s="0"/>
+      <c r="AHD1" s="0"/>
+      <c r="AHE1" s="0"/>
+      <c r="AHF1" s="0"/>
+      <c r="AHG1" s="0"/>
+      <c r="AHH1" s="0"/>
+      <c r="AHI1" s="0"/>
+      <c r="AHJ1" s="0"/>
+      <c r="AHK1" s="0"/>
+      <c r="AHL1" s="0"/>
+      <c r="AHM1" s="0"/>
+      <c r="AHN1" s="0"/>
+      <c r="AHO1" s="0"/>
+      <c r="AHP1" s="0"/>
+      <c r="AHQ1" s="0"/>
+      <c r="AHR1" s="0"/>
+      <c r="AHS1" s="0"/>
+      <c r="AHT1" s="0"/>
+      <c r="AHU1" s="0"/>
+      <c r="AHV1" s="0"/>
+      <c r="AHW1" s="0"/>
+      <c r="AHX1" s="0"/>
+      <c r="AHY1" s="0"/>
+      <c r="AHZ1" s="0"/>
+      <c r="AIA1" s="0"/>
+      <c r="AIB1" s="0"/>
+      <c r="AIC1" s="0"/>
+      <c r="AID1" s="0"/>
+      <c r="AIE1" s="0"/>
+      <c r="AIF1" s="0"/>
+      <c r="AIG1" s="0"/>
+      <c r="AIH1" s="0"/>
+      <c r="AII1" s="0"/>
+      <c r="AIJ1" s="0"/>
+      <c r="AIK1" s="0"/>
+      <c r="AIL1" s="0"/>
+      <c r="AIM1" s="0"/>
+      <c r="AIN1" s="0"/>
+      <c r="AIO1" s="0"/>
+      <c r="AIP1" s="0"/>
+      <c r="AIQ1" s="0"/>
+      <c r="AIR1" s="0"/>
+      <c r="AIS1" s="0"/>
+      <c r="AIT1" s="0"/>
+      <c r="AIU1" s="0"/>
+      <c r="AIV1" s="0"/>
+      <c r="AIW1" s="0"/>
+      <c r="AIX1" s="0"/>
+      <c r="AIY1" s="0"/>
+      <c r="AIZ1" s="0"/>
+      <c r="AJA1" s="0"/>
+      <c r="AJB1" s="0"/>
+      <c r="AJC1" s="0"/>
+      <c r="AJD1" s="0"/>
+      <c r="AJE1" s="0"/>
+      <c r="AJF1" s="0"/>
+      <c r="AJG1" s="0"/>
+      <c r="AJH1" s="0"/>
+      <c r="AJI1" s="0"/>
+      <c r="AJJ1" s="0"/>
+      <c r="AJK1" s="0"/>
+      <c r="AJL1" s="0"/>
+      <c r="AJM1" s="0"/>
+      <c r="AJN1" s="0"/>
+      <c r="AJO1" s="0"/>
+      <c r="AJP1" s="0"/>
+      <c r="AJQ1" s="0"/>
+      <c r="AJR1" s="0"/>
+      <c r="AJS1" s="0"/>
+      <c r="AJT1" s="0"/>
+      <c r="AJU1" s="0"/>
+      <c r="AJV1" s="0"/>
+      <c r="AJW1" s="0"/>
+      <c r="AJX1" s="0"/>
+      <c r="AJY1" s="0"/>
+      <c r="AJZ1" s="0"/>
+      <c r="AKA1" s="0"/>
+      <c r="AKB1" s="0"/>
+      <c r="AKC1" s="0"/>
+      <c r="AKD1" s="0"/>
+      <c r="AKE1" s="0"/>
+      <c r="AKF1" s="0"/>
+      <c r="AKG1" s="0"/>
+      <c r="AKH1" s="0"/>
+      <c r="AKI1" s="0"/>
+      <c r="AKJ1" s="0"/>
+      <c r="AKK1" s="0"/>
+      <c r="AKL1" s="0"/>
+      <c r="AKM1" s="0"/>
+      <c r="AKN1" s="0"/>
+      <c r="AKO1" s="0"/>
+      <c r="AKP1" s="0"/>
+      <c r="AKQ1" s="0"/>
+      <c r="AKR1" s="0"/>
+      <c r="AKS1" s="0"/>
+      <c r="AKT1" s="0"/>
+      <c r="AKU1" s="0"/>
+      <c r="AKV1" s="0"/>
+      <c r="AKW1" s="0"/>
+      <c r="AKX1" s="0"/>
+      <c r="AKY1" s="0"/>
+      <c r="AKZ1" s="0"/>
+      <c r="ALA1" s="0"/>
+      <c r="ALB1" s="0"/>
+      <c r="ALC1" s="0"/>
+      <c r="ALD1" s="0"/>
+      <c r="ALE1" s="0"/>
+      <c r="ALF1" s="0"/>
+      <c r="ALG1" s="0"/>
+      <c r="ALH1" s="0"/>
+      <c r="ALI1" s="0"/>
+      <c r="ALJ1" s="0"/>
+      <c r="ALK1" s="0"/>
+      <c r="ALL1" s="0"/>
+      <c r="ALM1" s="0"/>
+      <c r="ALN1" s="0"/>
+      <c r="ALO1" s="0"/>
+      <c r="ALP1" s="0"/>
+      <c r="ALQ1" s="0"/>
+      <c r="ALR1" s="0"/>
+      <c r="ALS1" s="0"/>
+      <c r="ALT1" s="0"/>
+      <c r="ALU1" s="0"/>
+      <c r="ALV1" s="0"/>
+      <c r="ALW1" s="0"/>
+      <c r="ALX1" s="0"/>
+      <c r="ALY1" s="0"/>
+      <c r="ALZ1" s="0"/>
+      <c r="AMA1" s="0"/>
+      <c r="AMB1" s="0"/>
+      <c r="AMC1" s="0"/>
+      <c r="AMD1" s="0"/>
+      <c r="AME1" s="0"/>
+      <c r="AMF1" s="0"/>
+      <c r="AMG1" s="0"/>
+      <c r="AMH1" s="0"/>
+      <c r="AMI1" s="0"/>
+      <c r="AMJ1" s="0"/>
+      <c r="AMK1" s="0"/>
     </row>
-    <row r="2" customFormat="false" ht="24" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="E2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I2" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="0" t="s">
-        <v>125</v>
+      <c r="J2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>127</v>
+        <v>110</v>
+      </c>
+      <c r="N2" s="0" t="s">
+        <v>110</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q2" s="0" t="s">
         <v>130</v>
       </c>
+      <c r="Q2" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="R2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="S2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="S2" s="2" t="s">
         <v>133</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="E3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>28199</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>27</v>
+      <c r="J3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>143</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Q3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="S3" s="1"/>
+      <c r="R3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U3" s="4"/>
+      <c r="V3" s="0"/>
+      <c r="W3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M4" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M3" r:id="rId1" display="info@kunde1.de"/>
+    <hyperlink ref="N3" r:id="rId2" display="info-cc@kunde1.de"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
@@ -1373,154 +2570,154 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="1" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="E1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="J1" s="0" t="s">
+      <c r="F1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="K1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="N1" s="0" t="s">
+      <c r="M1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="K2" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="L2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="N2" s="0" t="s">
+      <c r="M2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="N3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
